--- a/evaluation_surveys/020_social_care_impact_measurement_evaluation_form--evaluation_surveys.xlsx
+++ b/evaluation_surveys/020_social_care_impact_measurement_evaluation_form--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -763,17 +763,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>impact_areas_choices</t>
+          <t>evaluation_questions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>service_user_receives_support_with_personal_care</t>
+          <t>what_was_the_quality_of_the_support_provided?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service user receives support with personal care</t>
+          <t>What was the quality of the support provided?</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what_was_the_quality_of_the_support_provided?</t>
+          <t>how_responsive_were_the_staff?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What was the quality of the support provided?</t>
+          <t>How responsive were the staff?</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>how_responsive_were_the_staff?</t>
+          <t>how_clear_were_the_support_options?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How responsive were the staff?</t>
+          <t>How clear were the support options?</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>how_clear_were_the_support_options?</t>
+          <t>how_well_did_your_needs_and_preferences_are_met?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How clear were the support options?</t>
+          <t>How well did your needs and preferences are met?</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,10 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>how_well_did_your_needs_and_preferences_are_met?</t>
+          <t>was_your_experience_with_the_service_user_friendly?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>How well did your needs and preferences are met?</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>evaluation_questions_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>was_your_experience_with_the_service_user_friendly?</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Was your experience with the service user friendly?</t>
         </is>
